--- a/3692 HK Hansoh.xlsx
+++ b/3692 HK Hansoh.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF52B02-A2C2-466D-BFED-3FF0DA2B5ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{210A7CA9-599C-4605-B85A-BB9761906B06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-50100" yWindow="2280" windowWidth="22875" windowHeight="18315" xr2:uid="{932E178C-2618-490A-9E75-A7D2FB8C4B93}"/>
+    <workbookView xWindow="350" yWindow="1040" windowWidth="20990" windowHeight="19840" xr2:uid="{932E178C-2618-490A-9E75-A7D2FB8C4B93}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -150,13 +150,13 @@
     <t>Employees</t>
   </si>
   <si>
-    <t>Q423</t>
-  </si>
-  <si>
     <t>Cash RMB</t>
   </si>
   <si>
     <t>Debt RMB</t>
+  </si>
+  <si>
+    <t>Q425</t>
   </si>
 </sst>
 </file>
@@ -284,7 +284,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -299,7 +299,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
@@ -619,15 +618,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6DE6A44-E087-4669-9C3D-6CC909AE9090}">
   <dimension ref="B2:K17"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.140625" customWidth="1"/>
-    <col min="2" max="2" width="33.42578125" customWidth="1"/>
-    <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.1796875" customWidth="1"/>
+    <col min="2" max="2" width="33.453125" customWidth="1"/>
+    <col min="9" max="9" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" s="7" t="s">
         <v>7</v>
       </c>
@@ -644,10 +643,10 @@
         <v>0</v>
       </c>
       <c r="J2" s="1">
-        <v>19.739999999999998</v>
-      </c>
-    </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
+        <v>32.18</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
@@ -659,13 +658,13 @@
         <v>1</v>
       </c>
       <c r="J3" s="11">
-        <v>5933.3500700000004</v>
+        <v>6055.1507000000001</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
@@ -678,42 +677,41 @@
       </c>
       <c r="J4" s="11">
         <f>+J2*J3</f>
-        <v>117124.3303818</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+        <v>194854.749526</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="G5" s="3"/>
       <c r="I5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J5" s="11">
-        <f>24857+684.706</f>
-        <v>25541.705999999998</v>
+        <f>31548.668+772.486</f>
+        <v>32321.154000000002</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G6" s="3"/>
       <c r="I6" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" s="11">
+        <v>40.500999999999998</v>
+      </c>
+      <c r="K6" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="11">
-        <f>4183.198+39.742</f>
-        <v>4222.9400000000005</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>34</v>
       </c>
@@ -727,10 +725,10 @@
       </c>
       <c r="J7" s="11">
         <f>+J4-J5+J6</f>
-        <v>95805.56438180001</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
+        <v>162574.09652599998</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" s="7"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -738,91 +736,62 @@
       <c r="F8" s="8"/>
       <c r="G8" s="9"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12" t="s">
+      <c r="D9" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
       <c r="G9" s="3"/>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
       <c r="G10" s="3"/>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
       <c r="G11" s="3"/>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
       <c r="G12" s="3"/>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
       <c r="G13" s="3"/>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
       <c r="G14" s="3"/>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
       <c r="G15" s="3"/>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" s="2"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
       <c r="G16" s="3"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="4"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
@@ -838,19 +807,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{656E3CEB-BDB3-4C6D-8679-6AF53640C1EF}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="7" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C2">
         <v>2019</v>
       </c>
@@ -871,27 +840,27 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="14" t="s">
+    <row r="3" spans="1:7" s="13" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="B3" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="13">
         <v>8682746</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="13">
         <v>8690234</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="13">
         <v>9935141</v>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="13">
         <v>9382410</v>
       </c>
-      <c r="G3" s="14">
+      <c r="G3" s="13">
         <v>10103806</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="11" t="s">
         <v>23</v>
       </c>
@@ -911,7 +880,7 @@
         <v>1030863</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="11" t="s">
         <v>24</v>
       </c>
@@ -936,7 +905,7 @@
         <v>9072943</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="11" t="s">
         <v>25</v>
       </c>
@@ -956,7 +925,7 @@
         <v>3531163</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
         <v>26</v>
       </c>
@@ -976,7 +945,7 @@
         <v>709844</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
         <v>27</v>
       </c>
@@ -996,7 +965,7 @@
         <v>2097046</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
         <v>28</v>
       </c>
@@ -1021,7 +990,7 @@
         <v>6338053</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
         <v>29</v>
       </c>
@@ -1046,7 +1015,7 @@
         <v>2734890</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
         <v>31</v>
       </c>
@@ -1066,7 +1035,7 @@
         <v>488652</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="s">
         <v>32</v>
       </c>
@@ -1091,28 +1060,28 @@
         <v>2246238</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="13">
-        <f t="shared" ref="D16:G16" si="3">+D3/C3-1</f>
+      <c r="D16" s="12">
+        <f t="shared" ref="D16:F16" si="3">+D3/C3-1</f>
         <v>8.6239998267823026E-4</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="12">
         <f t="shared" si="3"/>
         <v>0.14325356486373098</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="12">
         <f t="shared" si="3"/>
         <v>-5.563393614645229E-2</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="12">
         <f>+G3/F3-1</f>
         <v>7.6888134285327592E-2</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>36</v>
       </c>
